--- a/Assets/_OriginalData/Excel/Config/Common/IAPProduct.xlsx
+++ b/Assets/_OriginalData/Excel/Config/Common/IAPProduct.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26145" windowHeight="10440" tabRatio="530"/>
+    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-空则用道具配置表中的，不空用当前的</t>
+指定ui，空为保持原有
+</t>
         </r>
         <r>
           <rPr>
@@ -126,7 +127,8 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">单个商品指定的是icon
+礼包商品指定是是bg
 </t>
         </r>
       </text>
@@ -439,7 +441,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="304">
   <si>
     <t>商品ID</t>
   </si>
@@ -587,6 +589,9 @@
     <t>1000&amp;3&amp;3</t>
   </si>
   <si>
+    <t>bg_shop_bundle1</t>
+  </si>
+  <si>
     <t>com.starfish.minigame.an_bundle_12.99</t>
   </si>
   <si>
@@ -596,18 +601,27 @@
     <t>2400&amp;3&amp;3&amp;3&amp;3&amp;3</t>
   </si>
   <si>
+    <t>bg_shop_bundle_s</t>
+  </si>
+  <si>
     <t>com.starfish.minigame.an_bundle_23.99</t>
   </si>
   <si>
     <t>5200&amp;5&amp;5&amp;5&amp;5&amp;5</t>
   </si>
   <si>
+    <t>bg_shop_bundle_m</t>
+  </si>
+  <si>
     <t>com.starfish.minigame.an_bundle_54.99</t>
   </si>
   <si>
     <t>14000&amp;9&amp;9&amp;9&amp;9&amp;9</t>
   </si>
   <si>
+    <t>bg_shop_bundle_l</t>
+  </si>
+  <si>
     <t>com.starfish.minigame.an_bundle_99.99</t>
   </si>
   <si>
@@ -617,6 +631,9 @@
     <t>24000&amp;30&amp;30&amp;30&amp;30&amp;10&amp;10&amp;10&amp;10</t>
   </si>
   <si>
+    <t>bg_shop_bundle3</t>
+  </si>
+  <si>
     <t>com.starfish.minigame.an_coin_4.99</t>
   </si>
   <si>
@@ -1109,9 +1126,6 @@
     <t>sticker_squirrel</t>
   </si>
   <si>
-    <t>bg_shop_bundle1</t>
-  </si>
-  <si>
     <t>com.starfish.minigame.ios_bundle_12.99</t>
   </si>
   <si>
@@ -1121,27 +1135,18 @@
     <t>2400,3,3,3,3,3</t>
   </si>
   <si>
-    <t>bg_shop_bundle_s</t>
-  </si>
-  <si>
     <t>com.starfish.minigame.ios_bundle_23.99</t>
   </si>
   <si>
     <t>5200,5,5,5,5,5</t>
   </si>
   <si>
-    <t>bg_shop_bundle_m</t>
-  </si>
-  <si>
     <t>com.starfish.minigame.ios_bundle_54.99</t>
   </si>
   <si>
     <t>14000,9,9,9,9,9</t>
   </si>
   <si>
-    <t>bg_shop_bundle_l</t>
-  </si>
-  <si>
     <t>com.starfish.minigame.ios_bundle_99.99</t>
   </si>
   <si>
@@ -1149,9 +1154,6 @@
   </si>
   <si>
     <t>24000,30,30,30,30,10,10,10,10</t>
-  </si>
-  <si>
-    <t>bg_shop_bundle3</t>
   </si>
   <si>
     <t>com.starfish.minigame.ios_coin_4.99</t>
@@ -1613,12 +1615,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
@@ -1626,6 +1622,12 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -2816,12 +2818,14 @@
       <c r="J8" s="34">
         <v>102</v>
       </c>
-      <c r="K8" s="36"/>
+      <c r="K8" s="36" t="s">
+        <v>36</v>
+      </c>
       <c r="L8" s="36"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="30">
         <v>0</v>
@@ -2836,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H9" s="48">
         <v>3</v>
@@ -2850,12 +2854,14 @@
       <c r="J9" s="34">
         <v>103</v>
       </c>
-      <c r="K9" s="36"/>
+      <c r="K9" s="36" t="s">
+        <v>40</v>
+      </c>
       <c r="L9" s="36"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="30" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" s="30">
         <v>0</v>
@@ -2870,10 +2876,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H10" s="48">
         <v>3</v>
@@ -2884,12 +2890,14 @@
       <c r="J10" s="34">
         <v>104</v>
       </c>
-      <c r="K10" s="36"/>
+      <c r="K10" s="36" t="s">
+        <v>43</v>
+      </c>
       <c r="L10" s="36"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="30" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B11" s="30">
         <v>0</v>
@@ -2904,10 +2912,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H11" s="48">
         <v>3</v>
@@ -2918,12 +2926,14 @@
       <c r="J11" s="34">
         <v>105</v>
       </c>
-      <c r="K11" s="36"/>
+      <c r="K11" s="36" t="s">
+        <v>46</v>
+      </c>
       <c r="L11" s="36"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="30" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B12" s="30">
         <v>0</v>
@@ -2938,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H12" s="48">
         <v>3</v>
@@ -2952,12 +2962,14 @@
       <c r="J12" s="34">
         <v>106</v>
       </c>
-      <c r="K12" s="36"/>
+      <c r="K12" s="36" t="s">
+        <v>50</v>
+      </c>
       <c r="L12" s="36"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="33" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B13" s="33">
         <v>0</v>
@@ -2987,13 +2999,13 @@
         <v>107</v>
       </c>
       <c r="K13" s="37" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L13" s="37"/>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="33" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B14" s="33">
         <v>0</v>
@@ -3023,13 +3035,13 @@
         <v>108</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L14" s="37"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="33" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B15" s="33">
         <v>0</v>
@@ -3059,13 +3071,13 @@
         <v>109</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="L15" s="37"/>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="33" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B16" s="33">
         <v>0</v>
@@ -3095,13 +3107,13 @@
         <v>110</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L16" s="37"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="33" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B17" s="33">
         <v>0</v>
@@ -3131,13 +3143,13 @@
         <v>111</v>
       </c>
       <c r="K17" s="37" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L17" s="37"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="30" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B18" s="30">
         <v>0</v>
@@ -3150,16 +3162,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H18" s="48">
         <v>3</v>
       </c>
       <c r="I18" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="34">
         <v>112</v>
@@ -3169,7 +3181,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B19" s="30">
         <v>0</v>
@@ -3182,16 +3194,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G19" s="32" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H19" s="48">
         <v>3</v>
       </c>
       <c r="I19" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="34">
         <v>113</v>
@@ -3201,7 +3213,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="33" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B20" s="33">
         <v>0</v>
@@ -3235,7 +3247,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="33" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B21" s="33">
         <v>0</v>
@@ -3269,7 +3281,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="33" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B22" s="33">
         <v>0</v>
@@ -3303,7 +3315,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="33" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B23" s="33">
         <v>0</v>
@@ -3318,10 +3330,10 @@
         <v>20</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G23" s="35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H23" s="48">
         <v>3</v>
@@ -3337,7 +3349,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="33" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B24" s="33">
         <v>0</v>
@@ -3352,10 +3364,10 @@
         <v>30</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G24" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H24" s="48">
         <v>3</v>
@@ -3371,7 +3383,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="33" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B25" s="33">
         <v>0</v>
@@ -3386,10 +3398,10 @@
         <v>40</v>
       </c>
       <c r="F25" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G25" s="35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H25" s="48">
         <v>3</v>
@@ -3405,7 +3417,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="30" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B26" s="30">
         <v>0</v>
@@ -3439,7 +3451,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="30" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B27" s="30">
         <v>0</v>
@@ -3473,7 +3485,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="30" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B28" s="30">
         <v>0</v>
@@ -3507,7 +3519,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="30" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B29" s="30">
         <v>0</v>
@@ -3522,10 +3534,10 @@
         <v>20</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G29" s="32" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H29" s="48">
         <v>3</v>
@@ -3541,7 +3553,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="30" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B30" s="30">
         <v>0</v>
@@ -3556,10 +3568,10 @@
         <v>30</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G30" s="32" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H30" s="48">
         <v>3</v>
@@ -3575,7 +3587,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="30" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B31" s="30">
         <v>0</v>
@@ -3590,10 +3602,10 @@
         <v>40</v>
       </c>
       <c r="F31" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" s="32" t="s">
         <v>74</v>
-      </c>
-      <c r="G31" s="32" t="s">
-        <v>69</v>
       </c>
       <c r="H31" s="48">
         <v>3</v>
@@ -3609,7 +3621,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="33" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B32" s="33">
         <v>0</v>
@@ -3643,7 +3655,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="33" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B33" s="33">
         <v>0</v>
@@ -3677,7 +3689,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="33" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B34" s="33">
         <v>0</v>
@@ -3711,7 +3723,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="33" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B35" s="33">
         <v>0</v>
@@ -3726,10 +3738,10 @@
         <v>20</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G35" s="35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H35" s="48">
         <v>3</v>
@@ -3745,7 +3757,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B36" s="33">
         <v>0</v>
@@ -3760,10 +3772,10 @@
         <v>30</v>
       </c>
       <c r="F36" s="35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G36" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H36" s="48">
         <v>3</v>
@@ -3779,7 +3791,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="33" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B37" s="33">
         <v>0</v>
@@ -3794,10 +3806,10 @@
         <v>40</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G37" s="35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H37" s="48">
         <v>3</v>
@@ -3813,7 +3825,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="30" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B38" s="30">
         <v>0</v>
@@ -3847,7 +3859,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="30" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B39" s="30">
         <v>0</v>
@@ -3881,7 +3893,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="30" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B40" s="30">
         <v>0</v>
@@ -3915,7 +3927,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B41" s="30">
         <v>0</v>
@@ -3949,7 +3961,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="30" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B42" s="30">
         <v>0</v>
@@ -3964,10 +3976,10 @@
         <v>20</v>
       </c>
       <c r="F42" s="32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G42" s="32" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H42" s="48">
         <v>3</v>
@@ -3983,7 +3995,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="30" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B43" s="30">
         <v>0</v>
@@ -3998,10 +4010,10 @@
         <v>30</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G43" s="32" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H43" s="48">
         <v>3</v>
@@ -4017,7 +4029,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="30" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B44" s="30">
         <v>0</v>
@@ -4032,10 +4044,10 @@
         <v>40</v>
       </c>
       <c r="F44" s="32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G44" s="32" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H44" s="48">
         <v>3</v>
@@ -4051,7 +4063,7 @@
     </row>
     <row r="45" customFormat="1" spans="1:12">
       <c r="A45" s="33" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B45" s="33">
         <v>0</v>
@@ -4085,7 +4097,7 @@
     </row>
     <row r="46" customFormat="1" spans="1:12">
       <c r="A46" s="33" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B46" s="33">
         <v>0</v>
@@ -4119,7 +4131,7 @@
     </row>
     <row r="47" customFormat="1" spans="1:12">
       <c r="A47" s="33" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B47" s="33">
         <v>0</v>
@@ -4153,7 +4165,7 @@
     </row>
     <row r="48" customFormat="1" spans="1:12">
       <c r="A48" s="33" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B48" s="33">
         <v>0</v>
@@ -4187,7 +4199,7 @@
     </row>
     <row r="49" customFormat="1" spans="1:12">
       <c r="A49" s="33" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B49" s="33">
         <v>0</v>
@@ -4202,10 +4214,10 @@
         <v>20</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G49" s="35" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H49" s="48">
         <v>3</v>
@@ -4221,7 +4233,7 @@
     </row>
     <row r="50" customFormat="1" spans="1:12">
       <c r="A50" s="33" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B50" s="33">
         <v>0</v>
@@ -4236,10 +4248,10 @@
         <v>30</v>
       </c>
       <c r="F50" s="35" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G50" s="35" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H50" s="48">
         <v>3</v>
@@ -4255,7 +4267,7 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="33" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B51" s="33">
         <v>0</v>
@@ -4270,10 +4282,10 @@
         <v>40</v>
       </c>
       <c r="F51" s="35" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G51" s="35" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H51" s="48">
         <v>3</v>
@@ -4437,7 +4449,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="30" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B7" s="30">
         <v>0</v>
@@ -4467,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L7" s="36" t="s">
         <v>32</v>
@@ -4475,7 +4487,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="30" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B8" s="30">
         <v>0</v>
@@ -4505,15 +4517,15 @@
         <v>1</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L8" s="36" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="30" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B9" s="30">
         <v>0</v>
@@ -4543,10 +4555,10 @@
         <v>1</v>
       </c>
       <c r="K9" s="36" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L9" s="36" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -4633,7 +4645,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="30">
         <v>0</v>
@@ -4659,7 +4671,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="30" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B16" s="30">
         <v>0</v>
@@ -4685,7 +4697,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="30" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="30">
         <v>0</v>
@@ -4711,7 +4723,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="30" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B18" s="30">
         <v>0</v>
@@ -4751,7 +4763,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="30" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B20" s="30">
         <v>0</v>
@@ -4777,7 +4789,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="30" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B21" s="30">
         <v>0</v>
@@ -4803,7 +4815,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="30" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B22" s="30">
         <v>0</v>
@@ -4829,7 +4841,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="30" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B23" s="30">
         <v>0</v>
@@ -4855,7 +4867,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="30" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B24" s="30">
         <v>0</v>
@@ -4895,7 +4907,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="30" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B26" s="30">
         <v>0</v>
@@ -4915,7 +4927,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B27" s="30">
         <v>0</v>
@@ -4949,7 +4961,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="33" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B29" s="33">
         <v>0</v>
@@ -4979,13 +4991,13 @@
         <v>2</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L29" s="37"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="33" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B30" s="33">
         <v>0</v>
@@ -5015,13 +5027,13 @@
         <v>2</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L30" s="37"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="33" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B31" s="33">
         <v>0</v>
@@ -5051,13 +5063,13 @@
         <v>2</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L31" s="37"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="33" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B32" s="33">
         <v>0</v>
@@ -5072,10 +5084,10 @@
         <v>20</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G32" s="35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H32" s="34">
         <v>100</v>
@@ -5091,7 +5103,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="33" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B33" s="33">
         <v>0</v>
@@ -5106,10 +5118,10 @@
         <v>30</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H33" s="34">
         <v>100</v>
@@ -5125,7 +5137,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="33" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B34" s="33">
         <v>0</v>
@@ -5140,10 +5152,10 @@
         <v>40</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G34" s="35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H34" s="34">
         <v>100</v>
@@ -5159,7 +5171,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="30" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B35" s="30">
         <v>0</v>
@@ -5189,13 +5201,13 @@
         <v>2</v>
       </c>
       <c r="K35" s="36" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L35" s="36"/>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="30" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B36" s="30">
         <v>0</v>
@@ -5225,13 +5237,13 @@
         <v>2</v>
       </c>
       <c r="K36" s="36" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L36" s="36"/>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="30" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B37" s="30">
         <v>0</v>
@@ -5261,13 +5273,13 @@
         <v>2</v>
       </c>
       <c r="K37" s="36" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L37" s="36"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="30" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B38" s="30">
         <v>0</v>
@@ -5282,10 +5294,10 @@
         <v>20</v>
       </c>
       <c r="F38" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G38" s="32" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H38" s="31">
         <v>100</v>
@@ -5301,7 +5313,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="30" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B39" s="30">
         <v>0</v>
@@ -5316,10 +5328,10 @@
         <v>30</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G39" s="32" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H39" s="31">
         <v>100</v>
@@ -5335,7 +5347,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="30" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B40" s="30">
         <v>0</v>
@@ -5350,10 +5362,10 @@
         <v>40</v>
       </c>
       <c r="F40" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G40" s="32" t="s">
         <v>74</v>
-      </c>
-      <c r="G40" s="32" t="s">
-        <v>69</v>
       </c>
       <c r="H40" s="31">
         <v>100</v>
@@ -5383,7 +5395,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="33" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B42" s="33">
         <v>0</v>
@@ -5413,13 +5425,13 @@
         <v>2</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="33" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B43" s="33">
         <v>0</v>
@@ -5449,13 +5461,13 @@
         <v>2</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L43" s="37"/>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="33" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B44" s="33">
         <v>0</v>
@@ -5485,13 +5497,13 @@
         <v>2</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L44" s="37"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="33" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B45" s="33">
         <v>0</v>
@@ -5506,10 +5518,10 @@
         <v>20</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G45" s="35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H45" s="34">
         <v>100</v>
@@ -5525,7 +5537,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B46" s="33">
         <v>0</v>
@@ -5540,10 +5552,10 @@
         <v>30</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G46" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H46" s="34">
         <v>100</v>
@@ -5559,7 +5571,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="33" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B47" s="33">
         <v>0</v>
@@ -5574,10 +5586,10 @@
         <v>40</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G47" s="35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H47" s="34">
         <v>100</v>
@@ -5607,7 +5619,7 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="30" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B49" s="30">
         <v>0</v>
@@ -5637,13 +5649,13 @@
         <v>2</v>
       </c>
       <c r="K49" s="36" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L49" s="36"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="30" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B50" s="30">
         <v>0</v>
@@ -5673,13 +5685,13 @@
         <v>2</v>
       </c>
       <c r="K50" s="36" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L50" s="36"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="30" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B51" s="30">
         <v>0</v>
@@ -5709,13 +5721,13 @@
         <v>2</v>
       </c>
       <c r="K51" s="36" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L51" s="36"/>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B52" s="30"/>
       <c r="C52" s="31"/>
@@ -5737,7 +5749,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="30" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B53" s="30">
         <v>0</v>
@@ -5752,10 +5764,10 @@
         <v>20</v>
       </c>
       <c r="F53" s="32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G53" s="32" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H53" s="31">
         <v>100</v>
@@ -5771,7 +5783,7 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="30" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B54" s="30">
         <v>0</v>
@@ -5786,10 +5798,10 @@
         <v>30</v>
       </c>
       <c r="F54" s="32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G54" s="32" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H54" s="31">
         <v>100</v>
@@ -5805,7 +5817,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="30" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B55" s="30">
         <v>0</v>
@@ -5820,10 +5832,10 @@
         <v>40</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G55" s="32" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H55" s="31">
         <v>100</v>
@@ -5853,7 +5865,7 @@
     </row>
     <row r="57" customFormat="1" spans="1:12">
       <c r="A57" s="33" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B57" s="33">
         <v>0</v>
@@ -5883,13 +5895,13 @@
         <v>2</v>
       </c>
       <c r="K57" s="37" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L57" s="37"/>
     </row>
     <row r="58" customFormat="1" spans="1:12">
       <c r="A58" s="33" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B58" s="33">
         <v>0</v>
@@ -5919,13 +5931,13 @@
         <v>2</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L58" s="37"/>
     </row>
     <row r="59" customFormat="1" spans="1:12">
       <c r="A59" s="33" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B59" s="33">
         <v>0</v>
@@ -5955,13 +5967,13 @@
         <v>2</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L59" s="37"/>
     </row>
     <row r="60" customFormat="1" spans="1:12">
       <c r="A60" s="33" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B60" s="33">
         <v>0</v>
@@ -5995,7 +6007,7 @@
     </row>
     <row r="61" customFormat="1" spans="1:12">
       <c r="A61" s="33" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B61" s="33">
         <v>0</v>
@@ -6010,10 +6022,10 @@
         <v>20</v>
       </c>
       <c r="F61" s="35" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G61" s="35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H61" s="34">
         <v>100</v>
@@ -6029,7 +6041,7 @@
     </row>
     <row r="62" customFormat="1" spans="1:12">
       <c r="A62" s="33" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B62" s="33">
         <v>0</v>
@@ -6044,10 +6056,10 @@
         <v>30</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G62" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H62" s="34">
         <v>100</v>
@@ -6063,7 +6075,7 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="33" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B63" s="33">
         <v>1</v>
@@ -6078,10 +6090,10 @@
         <v>40</v>
       </c>
       <c r="F63" s="35" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G63" s="35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H63" s="34">
         <v>100</v>
@@ -6097,7 +6109,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="38" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B74" s="38">
         <v>1</v>
@@ -6127,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="39" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L74" s="39" t="s">
         <v>32</v>
@@ -6135,7 +6147,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="38" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B75" s="38">
         <v>1</v>
@@ -6165,15 +6177,15 @@
         <v>1</v>
       </c>
       <c r="K75" s="39" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L75" s="39" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="38" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B76" s="38">
         <v>1</v>
@@ -6203,15 +6215,15 @@
         <v>1</v>
       </c>
       <c r="K76" s="39" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L76" s="39" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="41" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B77" s="41">
         <v>1</v>
@@ -6241,13 +6253,13 @@
         <v>2</v>
       </c>
       <c r="K77" s="44" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L77" s="44"/>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="41" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B78" s="41">
         <v>1</v>
@@ -6277,13 +6289,13 @@
         <v>2</v>
       </c>
       <c r="K78" s="44" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L78" s="44"/>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="41" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B79" s="41">
         <v>1</v>
@@ -6313,13 +6325,13 @@
         <v>2</v>
       </c>
       <c r="K79" s="44" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L79" s="44"/>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="41" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B80" s="41">
         <v>1</v>
@@ -6334,10 +6346,10 @@
         <v>20</v>
       </c>
       <c r="F80" s="43" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G80" s="43" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H80" s="42">
         <v>100</v>
@@ -6353,7 +6365,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="41" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B81" s="41">
         <v>1</v>
@@ -6368,10 +6380,10 @@
         <v>30</v>
       </c>
       <c r="F81" s="43" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G81" s="43" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H81" s="42">
         <v>100</v>
@@ -6387,7 +6399,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="41" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B82" s="41">
         <v>1</v>
@@ -6402,10 +6414,10 @@
         <v>40</v>
       </c>
       <c r="F82" s="43" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G82" s="43" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H82" s="42">
         <v>100</v>
@@ -6421,7 +6433,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="38" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B83" s="38">
         <v>1</v>
@@ -6451,13 +6463,13 @@
         <v>2</v>
       </c>
       <c r="K83" s="45" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L83" s="45"/>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="38" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B84" s="38">
         <v>1</v>
@@ -6487,13 +6499,13 @@
         <v>2</v>
       </c>
       <c r="K84" s="45" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L84" s="45"/>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="38" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B85" s="38">
         <v>1</v>
@@ -6523,13 +6535,13 @@
         <v>2</v>
       </c>
       <c r="K85" s="45" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L85" s="45"/>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="38" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B86" s="38">
         <v>1</v>
@@ -6544,10 +6556,10 @@
         <v>20</v>
       </c>
       <c r="F86" s="40" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G86" s="40" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H86" s="39">
         <v>100</v>
@@ -6563,7 +6575,7 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="38" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B87" s="38">
         <v>1</v>
@@ -6578,10 +6590,10 @@
         <v>30</v>
       </c>
       <c r="F87" s="40" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H87" s="39">
         <v>100</v>
@@ -6597,7 +6609,7 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="38" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B88" s="38">
         <v>1</v>
@@ -6612,10 +6624,10 @@
         <v>40</v>
       </c>
       <c r="F88" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="G88" s="40" t="s">
         <v>74</v>
-      </c>
-      <c r="G88" s="40" t="s">
-        <v>69</v>
       </c>
       <c r="H88" s="39">
         <v>100</v>
@@ -6779,7 +6791,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="30" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B7" s="30">
         <v>0</v>
@@ -6809,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L7" s="36" t="s">
         <v>32</v>
@@ -6817,7 +6829,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="30" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B8" s="30">
         <v>0</v>
@@ -6847,15 +6859,15 @@
         <v>1</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L8" s="36" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="30" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B9" s="30">
         <v>0</v>
@@ -6885,10 +6897,10 @@
         <v>1</v>
       </c>
       <c r="K9" s="36" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L9" s="36" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -6975,7 +6987,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="30">
         <v>0</v>
@@ -7001,7 +7013,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="30" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B16" s="30">
         <v>0</v>
@@ -7027,7 +7039,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="30" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="30">
         <v>0</v>
@@ -7053,7 +7065,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="30" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B18" s="30">
         <v>0</v>
@@ -7093,7 +7105,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="30" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B20" s="30">
         <v>0</v>
@@ -7117,7 +7129,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="30" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B21" s="30">
         <v>0</v>
@@ -7141,7 +7153,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="30" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B22" s="30">
         <v>0</v>
@@ -7165,7 +7177,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="30" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B23" s="30">
         <v>0</v>
@@ -7189,7 +7201,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="30" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B24" s="30">
         <v>0</v>
@@ -7227,7 +7239,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="30" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B26" s="30">
         <v>0</v>
@@ -7245,7 +7257,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B27" s="30">
         <v>0</v>
@@ -7277,7 +7289,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="33" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B29" s="33">
         <v>0</v>
@@ -7307,13 +7319,13 @@
         <v>2</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L29" s="37"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="33" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B30" s="33">
         <v>0</v>
@@ -7343,13 +7355,13 @@
         <v>2</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L30" s="37"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="33" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B31" s="33">
         <v>0</v>
@@ -7379,13 +7391,13 @@
         <v>2</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L31" s="37"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="33" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B32" s="33">
         <v>0</v>
@@ -7400,10 +7412,10 @@
         <v>20</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G32" s="35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H32" s="34">
         <v>100</v>
@@ -7419,7 +7431,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="33" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B33" s="33">
         <v>0</v>
@@ -7434,10 +7446,10 @@
         <v>30</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H33" s="34">
         <v>100</v>
@@ -7453,7 +7465,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="33" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B34" s="33">
         <v>0</v>
@@ -7468,10 +7480,10 @@
         <v>40</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G34" s="35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H34" s="34">
         <v>100</v>
@@ -7487,7 +7499,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="30" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B35" s="30">
         <v>0</v>
@@ -7517,13 +7529,13 @@
         <v>2</v>
       </c>
       <c r="K35" s="36" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L35" s="36"/>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="30" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B36" s="30">
         <v>0</v>
@@ -7553,13 +7565,13 @@
         <v>2</v>
       </c>
       <c r="K36" s="36" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L36" s="36"/>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="30" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B37" s="30">
         <v>0</v>
@@ -7589,13 +7601,13 @@
         <v>2</v>
       </c>
       <c r="K37" s="36" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L37" s="36"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="30" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B38" s="30">
         <v>0</v>
@@ -7610,10 +7622,10 @@
         <v>20</v>
       </c>
       <c r="F38" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G38" s="32" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H38" s="31">
         <v>100</v>
@@ -7629,7 +7641,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="30" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B39" s="30">
         <v>0</v>
@@ -7644,10 +7656,10 @@
         <v>30</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G39" s="32" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H39" s="31">
         <v>100</v>
@@ -7663,7 +7675,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="30" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B40" s="30">
         <v>0</v>
@@ -7678,10 +7690,10 @@
         <v>40</v>
       </c>
       <c r="F40" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G40" s="32" t="s">
         <v>74</v>
-      </c>
-      <c r="G40" s="32" t="s">
-        <v>69</v>
       </c>
       <c r="H40" s="31">
         <v>100</v>
@@ -7711,7 +7723,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="33" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B42" s="33">
         <v>0</v>
@@ -7741,13 +7753,13 @@
         <v>2</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="33" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B43" s="33">
         <v>0</v>
@@ -7777,13 +7789,13 @@
         <v>2</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L43" s="37"/>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="33" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B44" s="33">
         <v>0</v>
@@ -7813,13 +7825,13 @@
         <v>2</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L44" s="37"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="33" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B45" s="33">
         <v>0</v>
@@ -7834,10 +7846,10 @@
         <v>20</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G45" s="35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H45" s="34">
         <v>100</v>
@@ -7853,7 +7865,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="33" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B46" s="33">
         <v>0</v>
@@ -7868,10 +7880,10 @@
         <v>30</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G46" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H46" s="34">
         <v>100</v>
@@ -7887,7 +7899,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="33" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B47" s="33">
         <v>0</v>
@@ -7902,10 +7914,10 @@
         <v>40</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G47" s="35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H47" s="34">
         <v>100</v>
@@ -7935,7 +7947,7 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="30" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B49" s="30">
         <v>0</v>
@@ -7965,13 +7977,13 @@
         <v>2</v>
       </c>
       <c r="K49" s="36" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L49" s="36"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="30" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B50" s="30">
         <v>0</v>
@@ -8001,13 +8013,13 @@
         <v>2</v>
       </c>
       <c r="K50" s="36" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L50" s="36"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="30" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B51" s="30">
         <v>0</v>
@@ -8037,13 +8049,13 @@
         <v>2</v>
       </c>
       <c r="K51" s="36" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L51" s="36"/>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="30" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B52" s="30"/>
       <c r="C52" s="31"/>
@@ -8063,7 +8075,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="30" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B53" s="30">
         <v>0</v>
@@ -8078,10 +8090,10 @@
         <v>20</v>
       </c>
       <c r="F53" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G53" s="32" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H53" s="31">
         <v>100</v>
@@ -8097,7 +8109,7 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="30" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B54" s="30">
         <v>0</v>
@@ -8112,10 +8124,10 @@
         <v>30</v>
       </c>
       <c r="F54" s="32" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G54" s="32" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H54" s="31">
         <v>100</v>
@@ -8131,7 +8143,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="30" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B55" s="30">
         <v>0</v>
@@ -8146,10 +8158,10 @@
         <v>40</v>
       </c>
       <c r="F55" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G55" s="32" t="s">
         <v>74</v>
-      </c>
-      <c r="G55" s="32" t="s">
-        <v>69</v>
       </c>
       <c r="H55" s="31">
         <v>100</v>
@@ -8179,7 +8191,7 @@
     </row>
     <row r="57" customFormat="1" spans="1:12">
       <c r="A57" s="33" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B57" s="33">
         <v>0</v>
@@ -8209,13 +8221,13 @@
         <v>2</v>
       </c>
       <c r="K57" s="37" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L57" s="37"/>
     </row>
     <row r="58" customFormat="1" spans="1:12">
       <c r="A58" s="33" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B58" s="33">
         <v>0</v>
@@ -8245,13 +8257,13 @@
         <v>2</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L58" s="37"/>
     </row>
     <row r="59" customFormat="1" spans="1:12">
       <c r="A59" s="33" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B59" s="33">
         <v>0</v>
@@ -8281,13 +8293,13 @@
         <v>2</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L59" s="37"/>
     </row>
     <row r="60" customFormat="1" spans="1:12">
       <c r="A60" s="33" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B60" s="33">
         <v>0</v>
@@ -8305,7 +8317,7 @@
         <v>2104</v>
       </c>
       <c r="G60" s="35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H60" s="34">
         <v>100</v>
@@ -8321,7 +8333,7 @@
     </row>
     <row r="61" customFormat="1" spans="1:12">
       <c r="A61" s="33" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B61" s="33">
         <v>0</v>
@@ -8336,10 +8348,10 @@
         <v>30</v>
       </c>
       <c r="F61" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G61" s="35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H61" s="34">
         <v>100</v>
@@ -8355,7 +8367,7 @@
     </row>
     <row r="62" customFormat="1" spans="1:12">
       <c r="A62" s="33" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B62" s="33">
         <v>0</v>
@@ -8370,10 +8382,10 @@
         <v>40</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G62" s="35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H62" s="34">
         <v>100</v>
@@ -8389,7 +8401,7 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="33" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B63" s="33">
         <v>1</v>
@@ -8404,10 +8416,10 @@
         <v>41</v>
       </c>
       <c r="F63" s="35" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G63" s="35" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H63" s="34">
         <v>101</v>
@@ -8423,7 +8435,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="38" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B74" s="38">
         <v>1</v>
@@ -8453,7 +8465,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="39" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L74" s="39" t="s">
         <v>32</v>
@@ -8461,7 +8473,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="38" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B75" s="38">
         <v>1</v>
@@ -8491,15 +8503,15 @@
         <v>1</v>
       </c>
       <c r="K75" s="39" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L75" s="39" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="38" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B76" s="38">
         <v>1</v>
@@ -8529,15 +8541,15 @@
         <v>1</v>
       </c>
       <c r="K76" s="39" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L76" s="39" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="41" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B77" s="41">
         <v>1</v>
@@ -8567,13 +8579,13 @@
         <v>2</v>
       </c>
       <c r="K77" s="44" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L77" s="44"/>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="41" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B78" s="41">
         <v>1</v>
@@ -8603,13 +8615,13 @@
         <v>2</v>
       </c>
       <c r="K78" s="44" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L78" s="44"/>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="41" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B79" s="41">
         <v>1</v>
@@ -8639,13 +8651,13 @@
         <v>2</v>
       </c>
       <c r="K79" s="44" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L79" s="44"/>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="41" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B80" s="41">
         <v>1</v>
@@ -8660,10 +8672,10 @@
         <v>20</v>
       </c>
       <c r="F80" s="43" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G80" s="43" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H80" s="42">
         <v>100</v>
@@ -8679,7 +8691,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="41" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B81" s="41">
         <v>1</v>
@@ -8694,10 +8706,10 @@
         <v>30</v>
       </c>
       <c r="F81" s="43" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G81" s="43" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H81" s="42">
         <v>100</v>
@@ -8713,7 +8725,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="41" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B82" s="41">
         <v>1</v>
@@ -8728,10 +8740,10 @@
         <v>40</v>
       </c>
       <c r="F82" s="43" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G82" s="43" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H82" s="42">
         <v>100</v>
@@ -8747,7 +8759,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="38" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B83" s="38">
         <v>1</v>
@@ -8777,13 +8789,13 @@
         <v>2</v>
       </c>
       <c r="K83" s="45" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L83" s="45"/>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="38" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B84" s="38">
         <v>1</v>
@@ -8813,13 +8825,13 @@
         <v>2</v>
       </c>
       <c r="K84" s="45" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L84" s="45"/>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="38" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B85" s="38">
         <v>1</v>
@@ -8849,13 +8861,13 @@
         <v>2</v>
       </c>
       <c r="K85" s="45" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L85" s="45"/>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="38" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B86" s="38">
         <v>1</v>
@@ -8870,10 +8882,10 @@
         <v>20</v>
       </c>
       <c r="F86" s="40" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G86" s="40" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H86" s="39">
         <v>100</v>
@@ -8889,7 +8901,7 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="38" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B87" s="38">
         <v>1</v>
@@ -8904,10 +8916,10 @@
         <v>30</v>
       </c>
       <c r="F87" s="40" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H87" s="39">
         <v>100</v>
@@ -8923,7 +8935,7 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="38" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B88" s="38">
         <v>1</v>
@@ -8938,10 +8950,10 @@
         <v>40</v>
       </c>
       <c r="F88" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="G88" s="40" t="s">
         <v>74</v>
-      </c>
-      <c r="G88" s="40" t="s">
-        <v>69</v>
       </c>
       <c r="H88" s="39">
         <v>100</v>
@@ -8991,126 +9003,126 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:20">
       <c r="A2" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="T2" s="24" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:20">
@@ -9177,7 +9189,7 @@
     </row>
     <row r="4" ht="16.5" spans="1:20">
       <c r="A4" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B4" s="4">
         <v>0</v>
@@ -9227,7 +9239,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:20">
       <c r="A5" s="10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B5" s="4">
         <v>0</v>
@@ -9239,10 +9251,10 @@
         <v>5.99</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G5" s="10">
         <v>30</v>
@@ -9267,10 +9279,10 @@
       </c>
       <c r="N5" s="10"/>
       <c r="O5" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
@@ -9281,7 +9293,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:20">
       <c r="A6" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B6" s="4">
         <v>0</v>
@@ -9293,10 +9305,10 @@
         <v>12.99</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G6" s="10">
         <v>40</v>
@@ -9321,10 +9333,10 @@
       </c>
       <c r="N6" s="10"/>
       <c r="O6" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>214</v>
+        <v>40</v>
       </c>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
@@ -9335,7 +9347,7 @@
     </row>
     <row r="7" ht="16.5" spans="1:20">
       <c r="A7" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B7" s="4">
         <v>0</v>
@@ -9347,10 +9359,10 @@
         <v>23.99</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G7" s="10">
         <v>50</v>
@@ -9375,10 +9387,10 @@
       </c>
       <c r="N7" s="10"/>
       <c r="O7" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>217</v>
+        <v>43</v>
       </c>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
@@ -9389,7 +9401,7 @@
     </row>
     <row r="8" ht="16.5" spans="1:20">
       <c r="A8" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -9401,10 +9413,10 @@
         <v>54.99</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G8" s="10">
         <v>60</v>
@@ -9429,10 +9441,10 @@
       </c>
       <c r="N8" s="10"/>
       <c r="O8" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
@@ -9443,7 +9455,7 @@
     </row>
     <row r="9" ht="16.5" spans="1:20">
       <c r="A9" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -9455,10 +9467,10 @@
         <v>99.99</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G9" s="10">
         <v>80</v>
@@ -9483,10 +9495,10 @@
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
@@ -11267,10 +11279,10 @@
         <v>5.99</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G50" s="10">
         <v>30</v>
@@ -11295,10 +11307,10 @@
       </c>
       <c r="N50" s="10"/>
       <c r="O50" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P50" s="10" t="s">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="Q50" s="10"/>
       <c r="R50" s="10"/>
@@ -11309,7 +11321,7 @@
     </row>
     <row r="51" ht="16.5" spans="1:20">
       <c r="A51" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B51" s="4">
         <v>1</v>
@@ -11321,10 +11333,10 @@
         <v>12.99</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G51" s="10">
         <v>40</v>
@@ -11349,10 +11361,10 @@
       </c>
       <c r="N51" s="10"/>
       <c r="O51" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>214</v>
+        <v>40</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -11363,7 +11375,7 @@
     </row>
     <row r="52" ht="16.5" spans="1:20">
       <c r="A52" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B52" s="4">
         <v>1</v>
@@ -11375,10 +11387,10 @@
         <v>23.99</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G52" s="10">
         <v>50</v>
@@ -11403,10 +11415,10 @@
       </c>
       <c r="N52" s="10"/>
       <c r="O52" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P52" s="10" t="s">
-        <v>217</v>
+        <v>43</v>
       </c>
       <c r="Q52" s="10"/>
       <c r="R52" s="10"/>
@@ -11417,7 +11429,7 @@
     </row>
     <row r="53" ht="16.5" spans="1:20">
       <c r="A53" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B53" s="4">
         <v>1</v>
@@ -11429,10 +11441,10 @@
         <v>54.99</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G53" s="10">
         <v>60</v>
@@ -11457,10 +11469,10 @@
       </c>
       <c r="N53" s="10"/>
       <c r="O53" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -11471,7 +11483,7 @@
     </row>
     <row r="54" ht="16.5" spans="1:20">
       <c r="A54" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B54" s="4">
         <v>1</v>
@@ -11483,10 +11495,10 @@
         <v>99.99</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G54" s="10">
         <v>80</v>
@@ -11511,10 +11523,10 @@
       </c>
       <c r="N54" s="10"/>
       <c r="O54" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="Q54" s="10"/>
       <c r="R54" s="10"/>
@@ -11525,7 +11537,7 @@
     </row>
     <row r="55" ht="16.5" spans="1:20">
       <c r="A55" s="9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B55" s="4">
         <v>1</v>
@@ -11575,7 +11587,7 @@
     </row>
     <row r="56" ht="16.5" spans="1:20">
       <c r="A56" s="9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B56" s="4">
         <v>1</v>
@@ -11625,7 +11637,7 @@
     </row>
     <row r="57" ht="16.5" spans="1:20">
       <c r="A57" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B57" s="4">
         <v>1</v>
@@ -11675,7 +11687,7 @@
     </row>
     <row r="58" ht="16.5" spans="1:20">
       <c r="A58" s="9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B58" s="4">
         <v>1</v>
@@ -11725,7 +11737,7 @@
     </row>
     <row r="59" ht="16.5" spans="1:20">
       <c r="A59" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B59" s="4">
         <v>1</v>
@@ -11775,7 +11787,7 @@
     </row>
     <row r="60" ht="16.5" spans="1:20">
       <c r="A60" s="10" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B60" s="4">
         <v>1</v>
@@ -11831,7 +11843,7 @@
     </row>
     <row r="61" ht="16.5" spans="1:20">
       <c r="A61" s="10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B61" s="4">
         <v>1</v>
@@ -12141,7 +12153,7 @@
     </row>
     <row r="68" ht="16.5" spans="1:20">
       <c r="A68" s="20" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B68" s="4">
         <v>1</v>
@@ -12183,7 +12195,7 @@
     </row>
     <row r="69" ht="16.5" spans="1:20">
       <c r="A69" s="20" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B69" s="4">
         <v>1</v>
@@ -12225,7 +12237,7 @@
     </row>
     <row r="70" ht="16.5" spans="1:20">
       <c r="A70" s="20" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B70" s="4">
         <v>1</v>
@@ -12267,7 +12279,7 @@
     </row>
     <row r="71" ht="16.5" spans="1:20">
       <c r="A71" s="20" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B71" s="4">
         <v>1</v>
@@ -12309,7 +12321,7 @@
     </row>
     <row r="72" ht="16.5" spans="1:20">
       <c r="A72" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B72" s="4">
         <v>1</v>
@@ -12351,7 +12363,7 @@
     </row>
     <row r="73" ht="16.5" spans="1:20">
       <c r="A73" s="20" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B73" s="4">
         <v>1</v>
@@ -12645,7 +12657,7 @@
     </row>
     <row r="80" ht="16.5" spans="1:20">
       <c r="A80" s="20" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B80" s="4">
         <v>1</v>
@@ -12687,7 +12699,7 @@
     </row>
     <row r="81" ht="16.5" spans="1:20">
       <c r="A81" s="20" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B81" s="4">
         <v>1</v>
@@ -12729,7 +12741,7 @@
     </row>
     <row r="82" ht="16.5" spans="1:20">
       <c r="A82" s="20" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B82" s="4">
         <v>1</v>
@@ -12771,7 +12783,7 @@
     </row>
     <row r="83" ht="16.5" spans="1:20">
       <c r="A83" s="20" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B83" s="4">
         <v>1</v>
@@ -12813,7 +12825,7 @@
     </row>
     <row r="84" ht="16.5" spans="1:20">
       <c r="A84" s="20" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B84" s="4">
         <v>1</v>
@@ -12855,7 +12867,7 @@
     </row>
     <row r="85" ht="16.5" spans="1:20">
       <c r="A85" s="20" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B85" s="4">
         <v>1</v>
@@ -12897,7 +12909,7 @@
     </row>
     <row r="86" ht="16.5" spans="1:20">
       <c r="A86" s="20" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B86" s="4">
         <v>1</v>
@@ -12939,7 +12951,7 @@
     </row>
     <row r="87" ht="16.5" spans="1:20">
       <c r="A87" s="22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B87" s="4">
         <v>1</v>
@@ -12981,7 +12993,7 @@
     </row>
     <row r="88" ht="16.5" spans="1:20">
       <c r="A88" s="22" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B88" s="4">
         <v>1</v>
@@ -13023,7 +13035,7 @@
     </row>
     <row r="89" ht="16.5" spans="1:20">
       <c r="A89" s="22" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B89" s="4">
         <v>1</v>
@@ -13065,7 +13077,7 @@
     </row>
     <row r="90" ht="16.5" spans="1:20">
       <c r="A90" s="22" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B90" s="4">
         <v>1</v>
@@ -13107,7 +13119,7 @@
     </row>
     <row r="91" ht="16.5" spans="1:20">
       <c r="A91" s="22" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B91" s="4">
         <v>1</v>
@@ -13149,7 +13161,7 @@
     </row>
     <row r="92" ht="16.5" spans="1:20">
       <c r="A92" s="22" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B92" s="4">
         <v>1</v>
@@ -13191,7 +13203,7 @@
     </row>
     <row r="93" ht="16.5" spans="1:20">
       <c r="A93" s="22" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B93" s="4">
         <v>1</v>
